--- a/public/downloads/Anexo_2_Lista_de_verificacion_auditoria_interna.xlsx
+++ b/public/downloads/Anexo_2_Lista_de_verificacion_auditoria_interna.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelicavaronquintero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{180D13E3-0E9F-E64C-BD14-DB078D3B9412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{687063B3-F9E7-43E4-86CB-8732F8A55393}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23055881-EF13-4E66-8A43-69013AEF7D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34200" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="3" activeTab="3" xr2:uid="{DF133B54-39BE-4E7E-8AA5-BF7D91982A12}"/>
+    <workbookView xWindow="-34200" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="2" activeTab="2" xr2:uid="{DF133B54-39BE-4E7E-8AA5-BF7D91982A12}"/>
   </bookViews>
   <sheets>
     <sheet name="EJEMPLO LISTA DE CHEQUEO 1" sheetId="1" r:id="rId1"/>
@@ -257,7 +257,7 @@
 Plan de auditoría.</t>
   </si>
   <si>
-    <t>No se evidencia seguimientos constanes en los procesos con puntas débiles o críticos.</t>
+    <t>No se evidencia seguimientos constantes en los procesos con puntas débiles o críticos.</t>
   </si>
 </sst>
 </file>
@@ -314,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -624,6 +624,174 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -631,7 +799,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -670,6 +838,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -698,6 +872,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
@@ -793,11 +973,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1131,244 +1356,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="38"/>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="50" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="39"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="52" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="55"/>
     </row>
     <row r="5" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="53" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="57" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="54"/>
+    <row r="6" spans="1:6" customFormat="1" ht="48" customHeight="1">
+      <c r="A6" s="74"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="75"/>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="73"/>
     </row>
     <row r="8" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="67"/>
     </row>
     <row r="9" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="29">
+      <c r="B9" s="30"/>
+      <c r="C9" s="33">
         <v>44113</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="67"/>
     </row>
     <row r="10" spans="1:6" s="3" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="31"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="33"/>
+      <c r="F10" s="69"/>
     </row>
     <row r="11" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="24"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="20"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="64"/>
     </row>
     <row r="13" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="20"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="20"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
       <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="64"/>
     </row>
     <row r="15" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="20"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
       <c r="D15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="22"/>
+      <c r="F15" s="64"/>
     </row>
     <row r="16" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="20"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="64"/>
     </row>
     <row r="17" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="20"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4"/>
       <c r="D17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="64"/>
     </row>
     <row r="18" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="20"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="6"/>
       <c r="D18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="64"/>
     </row>
     <row r="19" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="20"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="6"/>
       <c r="D19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="22"/>
-    </row>
-    <row r="20" spans="1:6" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A20" s="14" t="s">
+      <c r="F19" s="64"/>
+    </row>
+    <row r="20" spans="1:6" ht="49.5" customHeight="1">
+      <c r="A20" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="5" t="s">
+      <c r="B20" s="60"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="E20" s="61"/>
+      <c r="F20" s="62"/>
+    </row>
+    <row r="21" spans="1:6" ht="12.75">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1503,12 +1728,12 @@
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -1575,186 +1800,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="38"/>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="50" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="39"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="52" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="55"/>
     </row>
     <row r="5" spans="1:6" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="53" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="54"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
     </row>
     <row r="9" spans="1:6" ht="28.5" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" spans="1:6" s="3" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="31"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="33"/>
+      <c r="F10" s="37"/>
     </row>
     <row r="11" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
     </row>
     <row r="12" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
     </row>
     <row r="17" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="1:6" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8"/>
@@ -1891,12 +2116,12 @@
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -1963,111 +2188,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="38"/>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="50" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="51"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="3" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="39"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="52" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="51"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="53" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="54"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="29">
+      <c r="B9" s="30"/>
+      <c r="C9" s="33">
         <v>44113</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="31"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2077,16 +2302,16 @@
       <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="s">
         <v>39</v>
       </c>
@@ -2096,14 +2321,14 @@
       <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="20"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
@@ -2113,14 +2338,14 @@
       <c r="E12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="20"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4" t="s">
         <v>45</v>
       </c>
@@ -2130,16 +2355,16 @@
       <c r="E13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="24"/>
     </row>
     <row r="14" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="20"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4" t="s">
         <v>49</v>
       </c>
@@ -2149,14 +2374,14 @@
       <c r="E14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="20"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4" t="s">
         <v>52</v>
       </c>
@@ -2166,55 +2391,55 @@
       <c r="E15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="55" t="s">
+      <c r="F15" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="56"/>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="22"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
     </row>
     <row r="18" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24"/>
     </row>
     <row r="19" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="24"/>
     </row>
     <row r="20" spans="1:7" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="8"/>
@@ -2366,13 +2591,13 @@
       <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2439,105 +2664,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="38"/>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="50" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="51"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="3" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="39"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="52" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="51"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="1:7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="53" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="54"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="31"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2547,100 +2772,100 @@
       <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24"/>
     </row>
     <row r="14" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="22"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
     </row>
     <row r="18" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24"/>
     </row>
     <row r="19" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="24"/>
     </row>
     <row r="20" spans="1:7" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="8"/>
@@ -2792,13 +3017,13 @@
       <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2847,26 +3072,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13c90a0b-73bc-4dc0-be5f-28d77b615beb" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13c93bba-48ce-428c-bfe5-88b42c19b028">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006A81D6BD42E8DF4C91013959704817E1" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bf4f72ffd194f0963ff564daca6869f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="13c90a0b-73bc-4dc0-be5f-28d77b615beb" xmlns:ns3="13c93bba-48ce-428c-bfe5-88b42c19b028" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8718d6f4873a5b1392a45044efa78385" ns2:_="" ns3:_="">
     <xsd:import namespace="13c90a0b-73bc-4dc0-be5f-28d77b615beb"/>
@@ -3101,14 +3306,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13c90a0b-73bc-4dc0-be5f-28d77b615beb" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13c93bba-48ce-428c-bfe5-88b42c19b028">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A20DFFC-F66D-47EF-802B-3E6430B8F30E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AC7539C-D3EC-417D-9866-EAD59EEAFE3F}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B20CC7C-32D2-49FD-B1A6-C3B5771E4F50}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A20DFFC-F66D-47EF-802B-3E6430B8F30E}"/>
 </file>